--- a/xlsx/그린바이오산업_특수분류표_3차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_3차.xlsx
@@ -4,6 +4,7 @@
   <sheets>
     <sheet name="그린바이오산업 특수분류" sheetId="1" r:id="rId1"/>
     <sheet name="KSIC11 연계표" sheetId="2" r:id="rId2"/>
+    <sheet name="AFSC 연계표" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -19414,4 +19415,2157 @@
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="6" width="32" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="36" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="30" customWidth="1"/>
+    <col min="11" max="11" width="80" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GBSC-AFSC(농축산식품산업 특수분류) 연계표</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">주의</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">직접대응은 0개입니다. 모든 행은 부분대응(컨테이너)으로, AFSC 세세분류가 생명공학 직접기여 여부를 식별하지 못해 개별 사업체 확인이 필요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대분류 코드</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대분류 명칭</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중분류 코드</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중분류 명칭</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">소분류 코드</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">소분류 명칭</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AFSC 코드</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AFSC 세세분류 명칭</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">판정</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KSIC11 교차확인</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 생물자원 생산업</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 식물자원 생산업</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 종자·종묘 생산업</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21122</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">종자 및 묘목 생산업</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분대응</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01123 종자 및 묘목 생산업(핵심)</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">품종개발~종묘 생산 활동은 겹치나 생명공학 기술 적용 여부와 단계별 활동을 식별하지 못한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 생물자원 생산업</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 식물자원 생산업</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 소재 원료용 식물 생산업</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21151</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">인삼 재배업</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분대응</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01140 기타 작물 재배업(조건부)</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">천연물·기능성 소재의 대표 원료이나 유용성분 탐색·선발·개량에 생명공학기술 적용 요건이 없어 일반 재배와 구분되지 않는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 생물자원 생산업</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 식물자원 생산업</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 소재 원료용 식물 생산업</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21152</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">약용작물 재배업</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분대응</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01140 기타 작물 재배업(조건부)</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">위와 같다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 생물자원 생산업</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 곤충자원 생산업</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 곤충자원 생산업</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22610</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">식용곤충 사육업</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분대응</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01299 그 외 기타 축산업(핵심)</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정의가 "번식·증식·사육"뿐이라 계통·품종 선발·개량, 생명공학 기술 적용 여부를 구분하지 못한다. 용도(식용)는 속성으로 기록.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 생물자원 생산업</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 곤충자원 생산업</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 곤충자원 생산업</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22620</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사료용 곤충 사육업</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분대응</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01299 그 외 기타 축산업(핵심)</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">위와 같다(용도: 사료용).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 생물자원 생산업</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 곤충자원 생산업</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 곤충자원 생산업</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22690</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 곤충 사육업</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분대응</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01299 그 외 기타 축산업(핵심)</t>
+        </is>
+      </c>
+      <c r="K10" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">위와 같다. 애완·학습용(22630)은 220의 명시적 배제 대상이라 제외.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 생물자원 생산업</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 미생물 및 세포·조직자원 생산업</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 미생물자원 생산업</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31164</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">식품용 미생물 제조업</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분대응</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10839 기타 식품 첨가물 제조업(조건부)</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미생물 자체 생산은 겹치나 "식품용"에 한정된 부분집합이고, 발굴·제작·배양 기술의 직접기여를 보장하지 않는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="51" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 생물자원 생산업</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 그린바이오 생물자원 생산업</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">291</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 실험동물 생산업</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22900</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 축산업</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분대응·주의</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01299 그 외 기타 축산업(핵심)</t>
+        </is>
+      </c>
+      <c r="K12" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28 신규 판정. 세세분류 정의가 "실험용 쥐, …, 토끼, 개" 사육을 명시해 활동이 겹치지만, 여우·곰·사슴·양잠 등 비실험 축산과 한 코드에 묶여 있고 291의 유전형질 제작·미생물학적 품질규격 요건을 식별하지 못한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="51" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 생물자원 생산업</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 그린바이오 생물자원 생산업</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">299</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그 외 기타 그린바이오 생물자원 생산업</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22900</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 축산업</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분대응·주의</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01299 그 외 기타 축산업(조건부)</t>
+        </is>
+      </c>
+      <c r="K13" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-28 신규 판정. "환형동물(지렁이 등) 사육" 갈래만 299의 대표활동과 겹치며 291과 코드를 공유한다(해상도 한계). 수생 생물자원 갈래(KSIC 03211~03213)는 AFSC가 수산업을 포괄하지 않아 공백.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 제품 제조업</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 작물재배용 제품 제조업</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생물농약·생물방제제품 제조업</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11152</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농업용 생물 살균·살충제 및 식물보호제 제조업</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분대응</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20322 생물 살균·살충제 및 식물보호제 제조업(핵심)</t>
+        </is>
+      </c>
+      <c r="K14" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생물·미생물·식물 유효성분 활동은 겹치나 천연 무기화합물까지 포함하고 생물공정 직접기여 요건이 없다. 11151(화학 농약)은 311의 배제기준에 해당해 제외.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 제품 제조업</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 작물재배용 제품 제조업</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">312</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 비료 제조업</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11133</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">유기질 비료 제조업</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분대응</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20313 유기질 비료 및 상토 제조업(핵심)</t>
+        </is>
+      </c>
+      <c r="K15" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">발효공정 일부와 겹치나 일반 퇴비까지 포괄하는 컨테이너.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 제품 제조업</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 사료·사료첨가제 제조업</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">321</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 사료 제조업</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11161</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">축산용 배합사료 제조업</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분대응</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10902 배합 사료 제조업(핵심)</t>
+        </is>
+      </c>
+      <c r="K16" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">발효·효소·생물전환 공정 요건이 없어 일반 배합사료와 구분 불가. 정의에 "실험 동물용 배합사료"도 포함되나 사료 제조 활동이므로 291이 아닌 여기에 연계.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 제품 제조업</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 사료·사료첨가제 제조업</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">321</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 사료 제조업</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11162</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">축산용 단미사료 및 기타 사료 제조업</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분대응</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10903 단미사료 및 기타 사료 제조업(핵심)</t>
+        </is>
+      </c>
+      <c r="K17" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">위와 같다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 제품 제조업</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 사료·사료첨가제 제조업</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">322</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 사료첨가제 제조업</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11162</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">축산용 단미사료 및 기타 사료 제조업</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분대응</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10903 단미사료 및 기타 사료 제조업(핵심)</t>
+        </is>
+      </c>
+      <c r="K18" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AFSC는 사료와 첨가제를 나누지 않아 321과 코드를 공유한다(해상도 한계). "조제 보조사료"가 322 갈래.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="51" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 제품 제조업</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 식품원료·식품 제조업</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">331</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 식품원료·첨가물 제조업</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31169</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 식품 첨가물 제조업</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분대응</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10839 기타 식품 첨가물 제조업(핵심)</t>
+        </is>
+      </c>
+      <c r="K19" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">첨가물·효소(효모 포함) 갈래만 대응하고 원료·중간소재 갈래는 공백. 화학·천연을 구분하지 않는 컨테이너. 31164(식품용 미생물)는 미생물 자체 생산이므로 231에 연계.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 제품 제조업</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 식품원료·식품 제조업</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">332</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31111</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김치류 제조업</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분대응·주의</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10301 김치류 제조업(조건부)</t>
+        </is>
+      </c>
+      <c r="K20" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"발효"는 명시되나 332가 요구하는 특정 미생물·스타터와 문서화된 제어발효공정인지 구분 불가 — 통상 자연발효 다수로 배제 위험 높음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 제품 제조업</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 식품원료·식품 제조업</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">332</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31163</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">장류 제조업</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분대응·주의</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10833 장류 제조업(조건부)</t>
+        </is>
+      </c>
+      <c r="K21" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">위와 같다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 제품 제조업</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 식품원료·식품 제조업</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">332</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31211</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">탁주 및 약주 제조업</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분대응·주의</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11111 탁주 및 약주 제조업(조건부)</t>
+        </is>
+      </c>
+      <c r="K22" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">위와 같다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 제품 제조업</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 식품원료·식품 제조업</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">332</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31212</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">맥아 및 맥주 제조업</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분대응·주의</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11112 맥아 및 맥주 제조업(조건부)</t>
+        </is>
+      </c>
+      <c r="K23" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">위와 같다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 제품 제조업</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 식품원료·식품 제조업</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">332</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31219</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농산물 가공 기타 발효주 제조업</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분대응·주의</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11119 기타 발효주 제조업(조건부)</t>
+        </is>
+      </c>
+      <c r="K24" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">위와 같다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 제품 제조업</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 식품원료·식품 제조업</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">332</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31221</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">주정 제조업</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분대응·주의</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11121 주정 제조업(조건부)</t>
+        </is>
+      </c>
+      <c r="K25" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">위와 같다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 제품 제조업</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 식품원료·식품 제조업</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">333</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 건강기능식품 제조업</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31181</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">인삼식품 제조업</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분대응</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10895 인삼식품 제조업(조건부)</t>
+        </is>
+      </c>
+      <c r="K26" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">위와 같다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 제품 제조업</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 식품원료·식품 제조업</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">333</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 건강기능식품 제조업</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31183</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">건강 기능식품 제조업</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분대응</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10897 건강 기능식품 제조업(핵심)</t>
+        </is>
+      </c>
+      <c r="K27" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기능성 원료 사용은 겹치나 생명공학·생물공정 직접 기여 입증 요건이 없다 — 333 스스로 "건강기능식품이라는 이유만으로 자동 포함하지 않는다"고 경고.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 제품 제조업</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 동물용 의약품 제조업</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">341</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">동물용 백신 및 기타 예방·치료용 생물학적 제제 제조업</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11171</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">축산용 의약품 제조업</t>
+        </is>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분대응</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21230 동물용 의약품 제조업(핵심)</t>
+        </is>
+      </c>
+      <c r="K28" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">완제 약제품 제조 활동은 겹치나 생물학적 제제와 합성의약품을 구분하지 못한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 제품 제조업</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 동물용 의약품 제조업</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">341</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">동물용 백신 및 기타 예방·치료용 생물학적 제제 제조업</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11172</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">반려동물용 의약품 제조업</t>
+        </is>
+      </c>
+      <c r="I29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분대응</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21230 동물용 의약품 제조업(핵심)</t>
+        </is>
+      </c>
+      <c r="K29" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">위와 같다(대상: 반려동물).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 제품 제조업</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 동물용 의약품 제조업</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">349</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 그린바이오 동물용 의약품 제조업</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11171</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">축산용 의약품 제조업</t>
+        </is>
+      </c>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분대응</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21230 동물용 의약품 제조업(핵심)</t>
+        </is>
+      </c>
+      <c r="K30" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">341과 코드 공유(해상도 한계).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 제품 제조업</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 동물용 의약품 제조업</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">349</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 그린바이오 동물용 의약품 제조업</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11172</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">반려동물용 의약품 제조업</t>
+        </is>
+      </c>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분대응</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21230 동물용 의약품 제조업(핵심)</t>
+        </is>
+      </c>
+      <c r="K31" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">위와 같다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="51" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 제품 제조업</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 그린바이오 제품 제조업</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">391</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 비식용 중간소재 제조업</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33200</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">곤충 가공 기타 제품 제조업</t>
+        </is>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분대응·주의</t>
+        </is>
+      </c>
+      <c r="J32" s="9"/>
+      <c r="K32" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정의가 식용 목적에 방점이 있어 391의 비식용 요건과 충돌 — 곤충 유래 비식용 산업소재 생산분만 해당. 391의 KSIC 균형안에 대응 코드가 없어 삼각관계가 닫히지 않는 유일한 행.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 제품 제조업</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 그린바이오 제품 제조업</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">391</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 비식용 중간소재 제조업</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33910</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">동식물 유래 한약 및 한약제제 제조업</t>
+        </is>
+      </c>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분대응</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21220 한의약품 제조업(조건부)</t>
+        </is>
+      </c>
+      <c r="K33" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">천연물 유래 소재라는 점은 겹치나 생명공학기술 적용 요건이 없다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 제품 제조업</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 그린바이오 제품 제조업</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">392</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 향장·생활제품 제조업</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33920</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">동식물 유래 천연 및 유기농 화장품 제조업</t>
+        </is>
+      </c>
+      <c r="I34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분대응</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20423 화장품 제조업(핵심)</t>
+        </is>
+      </c>
+      <c r="K34" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">제품범위는 겹치나 생물공정 직접기여 요건이 없어 천연·유기농 표시만 있는 일반 화장품을 걸러내지 못한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 생물자원·제품 도소매업</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 생물자원·제품 도매업</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">410</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 생물자원·제품 도매업</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13116</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">종묘 도매업</t>
+        </is>
+      </c>
+      <c r="I35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분대응·주의</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46202 종자 및 묘목 도매업(핵심)</t>
+        </is>
+      </c>
+      <c r="K35" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">취급 대상은 겹치나 410은 생명공학 기술로 개발·확인된 재화만 요건으로 하고 일반 종자 도매를 명시적으로 제외해 배제 위험 높음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 관련 서비스업</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 관련 시험·인증 서비스업</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">541</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 시험·분석 서비스업</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89401</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농식품 관련 물질 성분 검사 및 분석, 인증업</t>
+        </is>
+      </c>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분대응</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72911 물질 성분 검사 및 분석업(핵심)</t>
+        </is>
+      </c>
+      <c r="K36" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검사·분석 활동은 겹치나 그린바이오 특화 여부 확인 필요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 관련 서비스업</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 관련 시험·인증 서비스업</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">541</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 시험·분석 서비스업</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89409</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 농산업 관련 시험, 검사 및 분석, 인증업</t>
+        </is>
+      </c>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분대응</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72919 기타 기술 시험, 검사 및 분석업(조건부)</t>
+        </is>
+      </c>
+      <c r="K37" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">위와 같다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 관련 서비스업</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 관련 시험·인증 서비스업</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">542</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 검사·인증 서비스업</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89401</t>
+        </is>
+      </c>
+      <c r="H38" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">농식품 관련 물질 성분 검사 및 분석, 인증업</t>
+        </is>
+      </c>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분대응</t>
+        </is>
+      </c>
+      <c r="J38" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72911 물질 성분 검사 및 분석업(핵심)</t>
+        </is>
+      </c>
+      <c r="K38" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">인증 활동은 겹치나 그린바이오 특화 여부 확인 필요. 541과 코드 공유(해상도 한계).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 관련 서비스업</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 관련 시험·인증 서비스업</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">542</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 검사·인증 서비스업</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89409</t>
+        </is>
+      </c>
+      <c r="H39" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기타 농산업 관련 시험, 검사 및 분석, 인증업</t>
+        </is>
+      </c>
+      <c r="I39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분대응</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72919 기타 기술 시험, 검사 및 분석업(조건부)</t>
+        </is>
+      </c>
+      <c r="K39" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">위와 같다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="62">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="A20:A25"/>
+    <mergeCell ref="B20:B25"/>
+    <mergeCell ref="C20:C25"/>
+    <mergeCell ref="D20:D25"/>
+    <mergeCell ref="E20:E25"/>
+    <mergeCell ref="F20:F25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="F38:F39"/>
+  </mergeCells>
+  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/xlsx/그린바이오산업_특수분류표_3차.xlsx
+++ b/xlsx/그린바이오산업_특수분류표_3차.xlsx
@@ -4,7 +4,6 @@
   <sheets>
     <sheet name="그린바이오산업 특수분류" sheetId="1" r:id="rId1"/>
     <sheet name="KSIC11 연계표" sheetId="2" r:id="rId2"/>
-    <sheet name="AFSC 연계표" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -19415,2157 +19414,4 @@
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="16.5"/>
-  <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="30" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="32" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="36" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="30" customWidth="1"/>
-    <col min="11" max="11" width="80" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GBSC-AFSC(농축산식품산업 특수분류) 연계표</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">주의</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">직접대응은 0개입니다. 모든 행은 부분대응(컨테이너)으로, AFSC 세세분류가 생명공학 직접기여 여부를 식별하지 못해 개별 사업체 확인이 필요합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대분류 코드</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대분류 명칭</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">중분류 코드</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">중분류 명칭</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">소분류 코드</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">소분류 명칭</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AFSC 코드</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AFSC 세세분류 명칭</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">판정</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KSIC11 교차확인</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생물자원 생산업</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식물자원 생산업</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 종자·종묘 생산업</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21122</t>
-        </is>
-      </c>
-      <c r="H5" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">종자 및 묘목 생산업</t>
-        </is>
-      </c>
-      <c r="I5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="J5" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01123 종자 및 묘목 생산업(핵심)</t>
-        </is>
-      </c>
-      <c r="K5" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">품종개발~종묘 생산 활동은 겹치나 생명공학 기술 적용 여부와 단계별 활동을 식별하지 못한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생물자원 생산업</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식물자원 생산업</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 소재 원료용 식물 생산업</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21151</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">인삼 재배업</t>
-        </is>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="J6" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01140 기타 작물 재배업(조건부)</t>
-        </is>
-      </c>
-      <c r="K6" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">천연물·기능성 소재의 대표 원료이나 유용성분 탐색·선발·개량에 생명공학기술 적용 요건이 없어 일반 재배와 구분되지 않는다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생물자원 생산업</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식물자원 생산업</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 소재 원료용 식물 생산업</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21152</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">약용작물 재배업</t>
-        </is>
-      </c>
-      <c r="I7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="J7" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01140 기타 작물 재배업(조건부)</t>
-        </is>
-      </c>
-      <c r="K7" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위와 같다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생물자원 생산업</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 곤충자원 생산업</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 곤충자원 생산업</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22610</t>
-        </is>
-      </c>
-      <c r="H8" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">식용곤충 사육업</t>
-        </is>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="J8" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01299 그 외 기타 축산업(핵심)</t>
-        </is>
-      </c>
-      <c r="K8" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정의가 "번식·증식·사육"뿐이라 계통·품종 선발·개량, 생명공학 기술 적용 여부를 구분하지 못한다. 용도(식용)는 속성으로 기록.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생물자원 생산업</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 곤충자원 생산업</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 곤충자원 생산업</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22620</t>
-        </is>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">사료용 곤충 사육업</t>
-        </is>
-      </c>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="J9" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01299 그 외 기타 축산업(핵심)</t>
-        </is>
-      </c>
-      <c r="K9" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위와 같다(용도: 사료용).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생물자원 생산업</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 곤충자원 생산업</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 곤충자원 생산업</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22690</t>
-        </is>
-      </c>
-      <c r="H10" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 곤충 사육업</t>
-        </is>
-      </c>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="J10" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01299 그 외 기타 축산업(핵심)</t>
-        </is>
-      </c>
-      <c r="K10" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위와 같다. 애완·학습용(22630)은 220의 명시적 배제 대상이라 제외.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생물자원 생산업</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 미생물 및 세포·조직자원 생산업</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">231</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 미생물자원 생산업</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31164</t>
-        </is>
-      </c>
-      <c r="H11" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">식품용 미생물 제조업</t>
-        </is>
-      </c>
-      <c r="I11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="J11" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10839 기타 식품 첨가물 제조업(조건부)</t>
-        </is>
-      </c>
-      <c r="K11" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">미생물 자체 생산은 겹치나 "식품용"에 한정된 부분집합이고, 발굴·제작·배양 기술의 직접기여를 보장하지 않는다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="51" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생물자원 생산업</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 생물자원 생산업</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">291</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 실험동물 생산업</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22900</t>
-        </is>
-      </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 축산업</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="J12" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01299 그 외 기타 축산업(핵심)</t>
-        </is>
-      </c>
-      <c r="K12" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-28 신규 판정. 세세분류 정의가 "실험용 쥐, …, 토끼, 개" 사육을 명시해 활동이 겹치지만, 여우·곰·사슴·양잠 등 비실험 축산과 한 코드에 묶여 있고 291의 유전형질 제작·미생물학적 품질규격 요건을 식별하지 못한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="51" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생물자원 생산업</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 생물자원 생산업</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">299</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그 외 기타 그린바이오 생물자원 생산업</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22900</t>
-        </is>
-      </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 축산업</t>
-        </is>
-      </c>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="J13" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01299 그 외 기타 축산업(조건부)</t>
-        </is>
-      </c>
-      <c r="K13" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-28 신규 판정. "환형동물(지렁이 등) 사육" 갈래만 299의 대표활동과 겹치며 291과 코드를 공유한다(해상도 한계). 수생 생물자원 갈래(KSIC 03211~03213)는 AFSC가 수산업을 포괄하지 않아 공백.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제품 제조업</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 작물재배용 제품 제조업</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">생물농약·생물방제제품 제조업</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11152</t>
-        </is>
-      </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">농업용 생물 살균·살충제 및 식물보호제 제조업</t>
-        </is>
-      </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="J14" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20322 생물 살균·살충제 및 식물보호제 제조업(핵심)</t>
-        </is>
-      </c>
-      <c r="K14" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">생물·미생물·식물 유효성분 활동은 겹치나 천연 무기화합물까지 포함하고 생물공정 직접기여 요건이 없다. 11151(화학 농약)은 311의 배제기준에 해당해 제외.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제품 제조업</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 작물재배용 제품 제조업</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">312</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 비료 제조업</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11133</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">유기질 비료 제조업</t>
-        </is>
-      </c>
-      <c r="I15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="J15" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20313 유기질 비료 및 상토 제조업(핵심)</t>
-        </is>
-      </c>
-      <c r="K15" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">발효공정 일부와 겹치나 일반 퇴비까지 포괄하는 컨테이너.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제품 제조업</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 사료·사료첨가제 제조업</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">321</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 사료 제조업</t>
-        </is>
-      </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11161</t>
-        </is>
-      </c>
-      <c r="H16" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">축산용 배합사료 제조업</t>
-        </is>
-      </c>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="J16" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10902 배합 사료 제조업(핵심)</t>
-        </is>
-      </c>
-      <c r="K16" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">발효·효소·생물전환 공정 요건이 없어 일반 배합사료와 구분 불가. 정의에 "실험 동물용 배합사료"도 포함되나 사료 제조 활동이므로 291이 아닌 여기에 연계.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제품 제조업</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 사료·사료첨가제 제조업</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">321</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 사료 제조업</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11162</t>
-        </is>
-      </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">축산용 단미사료 및 기타 사료 제조업</t>
-        </is>
-      </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="J17" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10903 단미사료 및 기타 사료 제조업(핵심)</t>
-        </is>
-      </c>
-      <c r="K17" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위와 같다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="36" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제품 제조업</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 사료·사료첨가제 제조업</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">322</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 사료첨가제 제조업</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11162</t>
-        </is>
-      </c>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">축산용 단미사료 및 기타 사료 제조업</t>
-        </is>
-      </c>
-      <c r="I18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="J18" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10903 단미사료 및 기타 사료 제조업(핵심)</t>
-        </is>
-      </c>
-      <c r="K18" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AFSC는 사료와 첨가제를 나누지 않아 321과 코드를 공유한다(해상도 한계). "조제 보조사료"가 322 갈래.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="51" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제품 제조업</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품원료·식품 제조업</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">331</t>
-        </is>
-      </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품원료·첨가물 제조업</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31169</t>
-        </is>
-      </c>
-      <c r="H19" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 식품 첨가물 제조업</t>
-        </is>
-      </c>
-      <c r="I19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="J19" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10839 기타 식품 첨가물 제조업(핵심)</t>
-        </is>
-      </c>
-      <c r="K19" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">첨가물·효소(효모 포함) 갈래만 대응하고 원료·중간소재 갈래는 공백. 화학·천연을 구분하지 않는 컨테이너. 31164(식품용 미생물)는 미생물 자체 생산이므로 231에 연계.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="36" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제품 제조업</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품원료·식품 제조업</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">332</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31111</t>
-        </is>
-      </c>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">김치류 제조업</t>
-        </is>
-      </c>
-      <c r="I20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="J20" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10301 김치류 제조업(조건부)</t>
-        </is>
-      </c>
-      <c r="K20" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"발효"는 명시되나 332가 요구하는 특정 미생물·스타터와 문서화된 제어발효공정인지 구분 불가 — 통상 자연발효 다수로 배제 위험 높음.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제품 제조업</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품원료·식품 제조업</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">332</t>
-        </is>
-      </c>
-      <c r="F21" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31163</t>
-        </is>
-      </c>
-      <c r="H21" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">장류 제조업</t>
-        </is>
-      </c>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="J21" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10833 장류 제조업(조건부)</t>
-        </is>
-      </c>
-      <c r="K21" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위와 같다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제품 제조업</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품원료·식품 제조업</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">332</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31211</t>
-        </is>
-      </c>
-      <c r="H22" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">탁주 및 약주 제조업</t>
-        </is>
-      </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="J22" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11111 탁주 및 약주 제조업(조건부)</t>
-        </is>
-      </c>
-      <c r="K22" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위와 같다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제품 제조업</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품원료·식품 제조업</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">332</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31212</t>
-        </is>
-      </c>
-      <c r="H23" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">맥아 및 맥주 제조업</t>
-        </is>
-      </c>
-      <c r="I23" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="J23" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11112 맥아 및 맥주 제조업(조건부)</t>
-        </is>
-      </c>
-      <c r="K23" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위와 같다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제품 제조업</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품원료·식품 제조업</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">332</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31219</t>
-        </is>
-      </c>
-      <c r="H24" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">농산물 가공 기타 발효주 제조업</t>
-        </is>
-      </c>
-      <c r="I24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="J24" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11119 기타 발효주 제조업(조건부)</t>
-        </is>
-      </c>
-      <c r="K24" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위와 같다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제품 제조업</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품원료·식품 제조업</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">332</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31221</t>
-        </is>
-      </c>
-      <c r="H25" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">주정 제조업</t>
-        </is>
-      </c>
-      <c r="I25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="J25" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11121 주정 제조업(조건부)</t>
-        </is>
-      </c>
-      <c r="K25" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위와 같다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제품 제조업</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품원료·식품 제조업</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">333</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 건강기능식품 제조업</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31181</t>
-        </is>
-      </c>
-      <c r="H26" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">인삼식품 제조업</t>
-        </is>
-      </c>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="J26" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10895 인삼식품 제조업(조건부)</t>
-        </is>
-      </c>
-      <c r="K26" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위와 같다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="36" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제품 제조업</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식품원료·식품 제조업</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">333</t>
-        </is>
-      </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 건강기능식품 제조업</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31183</t>
-        </is>
-      </c>
-      <c r="H27" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">건강 기능식품 제조업</t>
-        </is>
-      </c>
-      <c r="I27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="J27" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10897 건강 기능식품 제조업(핵심)</t>
-        </is>
-      </c>
-      <c r="K27" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기능성 원료 사용은 겹치나 생명공학·생물공정 직접 기여 입증 요건이 없다 — 333 스스로 "건강기능식품이라는 이유만으로 자동 포함하지 않는다"고 경고.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제품 제조업</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 제조업</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">341</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">동물용 백신 및 기타 예방·치료용 생물학적 제제 제조업</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11171</t>
-        </is>
-      </c>
-      <c r="H28" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">축산용 의약품 제조업</t>
-        </is>
-      </c>
-      <c r="I28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="J28" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21230 동물용 의약품 제조업(핵심)</t>
-        </is>
-      </c>
-      <c r="K28" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">완제 약제품 제조 활동은 겹치나 생물학적 제제와 합성의약품을 구분하지 못한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제품 제조업</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 제조업</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">341</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">동물용 백신 및 기타 예방·치료용 생물학적 제제 제조업</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11172</t>
-        </is>
-      </c>
-      <c r="H29" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">반려동물용 의약품 제조업</t>
-        </is>
-      </c>
-      <c r="I29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="J29" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21230 동물용 의약품 제조업(핵심)</t>
-        </is>
-      </c>
-      <c r="K29" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위와 같다(대상: 반려동물).</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제품 제조업</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 제조업</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">349</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 동물용 의약품 제조업</t>
-        </is>
-      </c>
-      <c r="G30" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11171</t>
-        </is>
-      </c>
-      <c r="H30" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">축산용 의약품 제조업</t>
-        </is>
-      </c>
-      <c r="I30" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="J30" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21230 동물용 의약품 제조업(핵심)</t>
-        </is>
-      </c>
-      <c r="K30" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">341과 코드 공유(해상도 한계).</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제품 제조업</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 제조업</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">349</t>
-        </is>
-      </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 동물용 의약품 제조업</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11172</t>
-        </is>
-      </c>
-      <c r="H31" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">반려동물용 의약품 제조업</t>
-        </is>
-      </c>
-      <c r="I31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="J31" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21230 동물용 의약품 제조업(핵심)</t>
-        </is>
-      </c>
-      <c r="K31" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위와 같다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="51" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제품 제조업</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 제품 제조업</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">391</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 비식용 중간소재 제조업</t>
-        </is>
-      </c>
-      <c r="G32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33200</t>
-        </is>
-      </c>
-      <c r="H32" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">곤충 가공 기타 제품 제조업</t>
-        </is>
-      </c>
-      <c r="I32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="J32" s="9"/>
-      <c r="K32" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정의가 식용 목적에 방점이 있어 391의 비식용 요건과 충돌 — 곤충 유래 비식용 산업소재 생산분만 해당. 391의 KSIC 균형안에 대응 코드가 없어 삼각관계가 닫히지 않는 유일한 행.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제품 제조업</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 제품 제조업</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">391</t>
-        </is>
-      </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 비식용 중간소재 제조업</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33910</t>
-        </is>
-      </c>
-      <c r="H33" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">동식물 유래 한약 및 한약제제 제조업</t>
-        </is>
-      </c>
-      <c r="I33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="J33" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21220 한의약품 제조업(조건부)</t>
-        </is>
-      </c>
-      <c r="K33" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">천연물 유래 소재라는 점은 겹치나 생명공학기술 적용 요건이 없다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="36" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제품 제조업</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 제품 제조업</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">392</t>
-        </is>
-      </c>
-      <c r="F34" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 향장·생활제품 제조업</t>
-        </is>
-      </c>
-      <c r="G34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33920</t>
-        </is>
-      </c>
-      <c r="H34" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">동식물 유래 천연 및 유기농 화장품 제조업</t>
-        </is>
-      </c>
-      <c r="I34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="J34" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20423 화장품 제조업(핵심)</t>
-        </is>
-      </c>
-      <c r="K34" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">제품범위는 겹치나 생물공정 직접기여 요건이 없어 천연·유기농 표시만 있는 일반 화장품을 걸러내지 못한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="36" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생물자원·제품 도소매업</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생물자원·제품 도매업</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">410</t>
-        </is>
-      </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생물자원·제품 도매업</t>
-        </is>
-      </c>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13116</t>
-        </is>
-      </c>
-      <c r="H35" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">종묘 도매업</t>
-        </is>
-      </c>
-      <c r="I35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응·주의</t>
-        </is>
-      </c>
-      <c r="J35" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46202 종자 및 묘목 도매업(핵심)</t>
-        </is>
-      </c>
-      <c r="K35" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">취급 대상은 겹치나 410은 생명공학 기술로 개발·확인된 재화만 요건으로 하고 일반 종자 도매를 명시적으로 제외해 배제 위험 높음.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 관련 서비스업</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">54</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 관련 시험·인증 서비스업</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">541</t>
-        </is>
-      </c>
-      <c r="F36" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 시험·분석 서비스업</t>
-        </is>
-      </c>
-      <c r="G36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">89401</t>
-        </is>
-      </c>
-      <c r="H36" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">농식품 관련 물질 성분 검사 및 분석, 인증업</t>
-        </is>
-      </c>
-      <c r="I36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="J36" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72911 물질 성분 검사 및 분석업(핵심)</t>
-        </is>
-      </c>
-      <c r="K36" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">검사·분석 활동은 겹치나 그린바이오 특화 여부 확인 필요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 관련 서비스업</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">54</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 관련 시험·인증 서비스업</t>
-        </is>
-      </c>
-      <c r="E37" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">541</t>
-        </is>
-      </c>
-      <c r="F37" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 시험·분석 서비스업</t>
-        </is>
-      </c>
-      <c r="G37" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">89409</t>
-        </is>
-      </c>
-      <c r="H37" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 농산업 관련 시험, 검사 및 분석, 인증업</t>
-        </is>
-      </c>
-      <c r="I37" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="J37" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72919 기타 기술 시험, 검사 및 분석업(조건부)</t>
-        </is>
-      </c>
-      <c r="K37" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위와 같다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="36" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 관련 서비스업</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">54</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 관련 시험·인증 서비스업</t>
-        </is>
-      </c>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">542</t>
-        </is>
-      </c>
-      <c r="F38" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 검사·인증 서비스업</t>
-        </is>
-      </c>
-      <c r="G38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">89401</t>
-        </is>
-      </c>
-      <c r="H38" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">농식품 관련 물질 성분 검사 및 분석, 인증업</t>
-        </is>
-      </c>
-      <c r="I38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="J38" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72911 물질 성분 검사 및 분석업(핵심)</t>
-        </is>
-      </c>
-      <c r="K38" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">인증 활동은 겹치나 그린바이오 특화 여부 확인 필요. 541과 코드 공유(해상도 한계).</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 관련 서비스업</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">54</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 관련 시험·인증 서비스업</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">542</t>
-        </is>
-      </c>
-      <c r="F39" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 검사·인증 서비스업</t>
-        </is>
-      </c>
-      <c r="G39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">89409</t>
-        </is>
-      </c>
-      <c r="H39" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 농산업 관련 시험, 검사 및 분석, 인증업</t>
-        </is>
-      </c>
-      <c r="I39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분대응</t>
-        </is>
-      </c>
-      <c r="J39" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72919 기타 기술 시험, 검사 및 분석업(조건부)</t>
-        </is>
-      </c>
-      <c r="K39" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위와 같다.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="62">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B2:K2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="A20:A25"/>
-    <mergeCell ref="B20:B25"/>
-    <mergeCell ref="C20:C25"/>
-    <mergeCell ref="D20:D25"/>
-    <mergeCell ref="E20:E25"/>
-    <mergeCell ref="F20:F25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="F38:F39"/>
-  </mergeCells>
-  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
-</worksheet>
 </file>